--- a/en/data-mobilization/modules/ROOT/attachments/UC-Practice-1-ForCapture-template.xlsx
+++ b/en/data-mobilization/modules/ROOT/attachments/UC-Practice-1-ForCapture-template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856C0F71-4E6A-4540-A02B-7D281BEED9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="1920" windowWidth="25600" windowHeight="14320" xr2:uid="{A16DD252-91C3-C149-B0EA-EAAC784FD77A}"/>
+    <workbookView xWindow="25800" yWindow="1680" windowWidth="25600" windowHeight="14320" xr2:uid="{A16DD252-91C3-C149-B0EA-EAAC784FD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="butterfly-event" sheetId="1" r:id="rId1"/>
@@ -1127,12 +1127,6 @@
     <xf numFmtId="49" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1185,6 +1179,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5330,7 +5330,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
@@ -5586,30 +5586,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="50"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:2" ht="85" x14ac:dyDescent="0.2">
-      <c r="A3" s="33"/>
-      <c r="B3" s="35" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="33" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="33"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="34"/>
     </row>
     <row r="5" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="36" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5617,121 +5617,121 @@
       <c r="A6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="37" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="26"/>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="26"/>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="39" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="26"/>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="38" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="26"/>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="38" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="26"/>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="26"/>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="40" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="41"/>
     </row>
     <row r="14" spans="1:2" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="37" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="44"/>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="42"/>
+      <c r="B15" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="43"/>
-      <c r="B16" s="41" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="39" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="43"/>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="43"/>
-      <c r="B18" s="40" t="s">
+      <c r="A18" s="41"/>
+      <c r="B18" s="38" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="43"/>
-      <c r="B19" s="42" t="s">
+      <c r="A19" s="41"/>
+      <c r="B19" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
     </row>
     <row r="21" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="45" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="46"/>
+      <c r="B22" s="47" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="48"/>
-      <c r="B23" s="47" t="s">
+      <c r="A23" s="46"/>
+      <c r="B23" s="45" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="48"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="46"/>
+      <c r="B24" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="48"/>
-      <c r="B25" s="47" t="s">
+      <c r="A25" s="46"/>
+      <c r="B25" s="45" t="s">
         <v>53</v>
       </c>
     </row>
